--- a/reports/test_results.xlsx
+++ b/reports/test_results.xlsx
@@ -423,12 +423,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
   </cols>
@@ -468,12 +468,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>test_add_job_title</t>
+          <t>test_login_invalid_credentials</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>No description provided</t>
+          <t>Verify that an error message is displayed when attempting to log in with invalid credentials.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -495,22 +495,33 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>test_edit_job_title</t>
+          <t>test_login_empty_username</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No description provided</t>
+          <t>Verify that an error message is displayed when attempting to log in with an empty username.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Test Passed Successfully</t>
+          <t>self = &lt;test_login.TestLogin object at 0x0000016587613ED0&gt;
+authenticated_page = &lt;Page url='https://opensource-demo.orangehrmlive.com/web/index.php/auth/login'&gt;
+    def test_login_empty_username(self, authenticated_page: Page):
+        """Verify that an error message is displayed when attempting to log in with an empty username."""
+        self.login_page.navigate(BASE_URL)
+        self.login_page.login("", PASSWORD)
+&gt;       assert self.login_page.is_input_error_displayed()
+E       assert False
+E        +  where False = is_input_error_displayed()
+E        +    where is_input_error_displayed = &lt;pages.login_page.LoginPage object at 0x0000016587DC8690&gt;.is_input_error_displayed
+E        +      where &lt;pages.login_page.LoginPage object at 0x0000016587DC8690&gt; = &lt;test_login.TestLogin object at 0x0000016587613ED0&gt;.login_page
+tests\test_login.py:26: AssertionError</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PASSED</t>
+          <t>FAILED</t>
         </is>
       </c>
     </row>
@@ -522,12 +533,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>test_delete_job_title</t>
+          <t>test_login_empty_password</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>No description provided</t>
+          <t>Verify that an error message is displayed when attempting to log in with an empty password.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -549,12 +560,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>test_add_job_title_duplicate</t>
+          <t>test_orangehrm_login</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No description provided</t>
+          <t>Verify that the user can successfully log in with valid credentials.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -576,34 +587,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>test_add_job_title_empty</t>
+          <t>test_add_user</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>No description provided</t>
+          <t>Verify that a new user can be successfully added with valid information.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>self = &lt;test_job_actions.TestJob object at 0x000001ECC78983B0&gt;
-authenticated_page = &lt;Page url='https://opensource-demo.orangehrmlive.com/web/index.php/admin/saveJobTitle'&gt;
-    def test_add_job_title_empty(self, authenticated_page: Page):
-        #self.job_page.navigate_to_job_titles()
-        authenticated_page.wait_for_timeout(2000)
-        self.job_page.page.click(self.job_page.add_button)
-        # Click save without filling title
-        self.job_page.page.click(self.job_page.save_button)
-        # Verify required field error
-&gt;       assert self.job_page.is_required_error_visible(), "Required field error message not visible!"
-               ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
-E       TypeError: JobPage.is_required_error_visible() missing 1 required positional argument: 'field_name'
-tests\test_job_actions.py:92: TypeError</t>
+          <t>Test Passed Successfully</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FAILED</t>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -615,35 +614,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>test_cancel_add_job</t>
+          <t>test_add_user_empty</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No description provided</t>
+          <t>Verify that mandatory field 'Required' errors are displayed when attempting to save an empty user form.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>self = &lt;test_job_actions.TestJob object at 0x000001ECC772DD00&gt;
-authenticated_page = &lt;Page url='https://opensource-demo.orangehrmlive.com/web/index.php/admin/saveJobTitle'&gt;
-    def test_cancel_add_job(self, authenticated_page: Page):
-        #self.job_page.navigate_to_job_titles()
-        authenticated_page.wait_for_timeout(2000)
-&gt;       self.job_page.page.click(self.job_page.add_button)
-tests\test_job_actions.py:100: 
-_ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _
-C:\Users\reshma.b\AppData\Local\Programs\Python\Python313\Lib\site-packages\playwright\sync_api\_generated.py:9958: in click
-    self._sync(
-C:\Users\reshma.b\AppData\Local\Programs\Python\Python313\Lib\site-packages\playwright\_impl\_page.py:854: in click
-    return await self._main_frame._click(**locals_to_params(locals()))
-           ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
-C:\Users\reshma.b\AppData\Local\Programs\Python\Python313\Lib\site-packages\playwright\_impl\_frame.p</t>
+          <t>Test Passed Successfully</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FAILED</t>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -655,37 +641,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>test_bulk_delete_job_titles</t>
+          <t>test_add_user_duplicate</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>No description provided</t>
+          <t>Verify that an error message is displayed when attempting to add a user with an existing username.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>self = &lt;test_job_actions.TestJob object at 0x000001ECC772D590&gt;
-authenticated_page = &lt;Page url='https://opensource-demo.orangehrmlive.com/web/index.php/admin/saveJobTitle'&gt;
-    def test_bulk_delete_job_titles(self, authenticated_page: Page):
-        #self.job_page.navigate_to_job_titles()
-        authenticated_page.wait_for_timeout(2000)
-        # Create some random job titles to delete
-        titles_to_create = [f"BulkDelete_{random.randint(1000, 9999)}" for _ in range(3)]
-        for title in titles_to_create:
-&gt;           self.job_page.add_job(title)
-tests\test_job_actions.py:118: 
-_ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _
-pages\job_page.py:46: in add_job
-    self.page.click(self.add_button)
-C:\Users\reshma.b\AppData\Local\Programs\Python\Python313\Lib\site-packages\playwright\sync_api\_generated.py:9958: in click
-    self._sync(
-C:\Users\reshma.b\AppData\Local\Programs\Python\Python313\Lib\site-packages\playwright\_impl\_page.py:854: in click</t>
+          <t>Test Passed Successfully</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FAILED</t>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -697,36 +668,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>test_upload_job_specification</t>
+          <t>test_add_user_password_mismatch</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No description provided</t>
+          <t>Verify that an error message is displayed when the 'Password' and 'Confirm Password' fields do not match.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>self = &lt;test_job_actions.TestJob object at 0x000001ECC7721D50&gt;
-authenticated_page = &lt;Page url='https://opensource-demo.orangehrmlive.com/web/index.php/admin/saveJobTitle'&gt;
-    def test_upload_job_specification(self, authenticated_page: Page):
-        import os
-       # self.job_page.navigate_to_job_titles()
-        authenticated_page.wait_for_timeout(2000)
-&gt;       self.job_page.page.click(self.job_page.add_button)
-tests\test_job_actions.py:138: 
-_ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _
-C:\Users\reshma.b\AppData\Local\Programs\Python\Python313\Lib\site-packages\playwright\sync_api\_generated.py:9958: in click
-    self._sync(
-C:\Users\reshma.b\AppData\Local\Programs\Python\Python313\Lib\site-packages\playwright\_impl\_page.py:854: in click
-    return await self._main_frame._click(**locals_to_params(locals()))
-           ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
-C:\Users\reshma.b\AppData\Local\Programs\Python\Python313\Lib\site-packag</t>
+          <t>Test Passed Successfully</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FAILED</t>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -738,36 +695,1264 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>test_add_user_password_policy</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Verify that the password policy (minimum length) is enforced when adding a user.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Test Passed Successfully</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>test_edit_user</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Verify that an existing user's role can be successfully updated.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Test Passed Successfully</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>test_disable_user</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Verify that a user's status can be changed to 'Disabled'.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Test Passed Successfully</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>test_bulk_delete_users</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Verify that multiple users can be selected and deleted simultaneously.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Test Passed Successfully</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>test_search_user_by_username</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Verify that users can be searched and found by their exact username.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Test Passed Successfully</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>test_search_user_by_role</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Verify that users can be filtered by their assigned 'User Role'.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Test Passed Successfully</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>test_search_user_by_status</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Verify that users can be filtered by their current 'Status' (Enabled/Disabled).</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Test Passed Successfully</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>test_search_non_existing_user</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Verify that a 'No Records Found' message is displayed when searching for a non-existent username.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Test Passed Successfully</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>test_delete_user</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Verify that a user can be successfully deleted from the system.</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Test Passed Successfully</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>test_add_job_title</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>No description provided</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Test Passed Successfully</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>test_edit_job_title</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>No description provided</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Test Passed Successfully</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>test_delete_job_title</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>No description provided</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Test Passed Successfully</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>test_add_job_title_duplicate</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>No description provided</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Test Passed Successfully</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>test_add_job_title_empty</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>No description provided</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Test Passed Successfully</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>test_cancel_add_job</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>No description provided</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Test Passed Successfully</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>test_bulk_delete_job_titles</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>No description provided</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Test Passed Successfully</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>test_upload_job_specification</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>No description provided</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Test Passed Successfully</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>test_upload_invalid_file_format</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>No description provided</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>self = &lt;test_job_actions.TestJob object at 0x000001ECC7722350&gt;
-authenticated_page = &lt;Page url='https://opensource-demo.orangehrmlive.com/web/index.php/admin/saveJobTitle'&gt;
-    def test_upload_invalid_file_format(self, authenticated_page: Page):
-        import os
-        #self.job_page.navigate_to_job_titles()
-        authenticated_page.wait_for_timeout(2000)
-&gt;       self.job_page.page.click(self.job_page.add_button)
-tests\test_job_actions.py:161: 
-_ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _
-C:\Users\reshma.b\AppData\Local\Programs\Python\Python313\Lib\site-packages\playwright\sync_api\_generated.py:9958: in click
-    self._sync(
-C:\Users\reshma.b\AppData\Local\Programs\Python\Python313\Lib\site-packages\playwright\_impl\_page.py:854: in click
-    return await self._main_frame._click(**locals_to_params(locals()))
-           ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
-C:\Users\reshma.b\AppData\Local\Programs\Python\Python313\Lib\site-pack</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>No description provided</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Test Passed Successfully</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>test_add_employment_status</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>No description provided</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Test Passed Successfully</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>test_edit_employment_status</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>No description provided</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Test Passed Successfully</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>test_add_employment_status_empty</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>No description provided</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Test Passed Successfully</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>test_add_duplicate_employment_status</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>No description provided</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Test Passed Successfully</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>test_delete_employment_status</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>No description provided</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Test Passed Successfully</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>test_bulk_delete_employment_status</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>No description provided</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Test Passed Successfully</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>test_add_job_category</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>No description provided</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Test Passed Successfully</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>test_edit_job_category</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>No description provided</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Test Passed Successfully</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>test_add_job_category_empty</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>No description provided</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Test Passed Successfully</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>test_add_duplicate_job_category</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>No description provided</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Test Passed Successfully</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>test_delete_job_category</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>No description provided</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Test Passed Successfully</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>test_bulk_delete_job_categories</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>No description provided</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Test Passed Successfully</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>test_add_work_shift</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>No description provided</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Test Passed Successfully</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>test_add_work_shift_with_employee</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>No description provided</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Test Passed Successfully</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>test_add_work_shift_empty</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>No description provided</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Test Passed Successfully</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>test_add_work_shift_without_time</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>No description provided</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Test Passed Successfully</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>test_add_work_shift_invalid_time_range</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>No description provided</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Test Passed Successfully</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>test_add_duplicate_work_shift</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>No description provided</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Test Passed Successfully</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>test_edit_work_shift</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>No description provided</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Test Passed Successfully</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>test_delete_work_shift</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>No description provided</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Test Passed Successfully</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>test_bulk_delete_work_shifts</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>No description provided</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Test Passed Successfully</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>test_edit_general_info</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Verify that organization phone and fax numbers can be successfully updated.</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Test Passed Successfully</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>test_general_info_mandatory_field</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Verify that 'Organization Name' is a mandatory field and shows a 'Required' error when empty.</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Test Passed Successfully</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>test_add_location</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Verify that a new location can be successfully added with all fields filled.</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Test Passed Successfully</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>test_add_location_mandatory_name</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Verify that the 'Name' field is mandatory when adding a location.</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Test Passed Successfully</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>test_add_location_mandatory_country</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Verify that the 'Country' field is mandatory when adding a location.</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Test Passed Successfully</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>test_edit_location</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Verify that an existing location's name can be successfully updated.</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Test Passed Successfully</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>test_delete_location</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Verify that a location can be successfully deleted.</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Test Passed Successfully</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>test_bulk_delete_locations</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Verify that multiple locations can be selected and deleted in bulk.</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Test Passed Successfully</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
     </row>

--- a/reports/test_results.xlsx
+++ b/reports/test_results.xlsx
@@ -429,7 +429,7 @@
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -505,23 +505,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>self = &lt;test_login.TestLogin object at 0x0000016587613ED0&gt;
-authenticated_page = &lt;Page url='https://opensource-demo.orangehrmlive.com/web/index.php/auth/login'&gt;
-    def test_login_empty_username(self, authenticated_page: Page):
-        """Verify that an error message is displayed when attempting to log in with an empty username."""
-        self.login_page.navigate(BASE_URL)
-        self.login_page.login("", PASSWORD)
-&gt;       assert self.login_page.is_input_error_displayed()
-E       assert False
-E        +  where False = is_input_error_displayed()
-E        +    where is_input_error_displayed = &lt;pages.login_page.LoginPage object at 0x0000016587DC8690&gt;.is_input_error_displayed
-E        +      where &lt;pages.login_page.LoginPage object at 0x0000016587DC8690&gt; = &lt;test_login.TestLogin object at 0x0000016587613ED0&gt;.login_page
-tests\test_login.py:26: AssertionError</t>
+          <t>Test Passed Successfully</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FAILED</t>
+          <t>PASSED</t>
         </is>
       </c>
     </row>

--- a/reports/test_results.xlsx
+++ b/reports/test_results.xlsx
@@ -581,7 +581,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Verify that a new user can be successfully added with valid information.</t>
+          <t>No description provided</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Verify that mandatory field 'Required' errors are displayed when attempting to save an empty user form.</t>
+          <t>No description provided</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Verify that an error message is displayed when attempting to add a user with an existing username.</t>
+          <t>No description provided</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Verify that an error message is displayed when the 'Password' and 'Confirm Password' fields do not match.</t>
+          <t>No description provided</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Verify that the password policy (minimum length) is enforced when adding a user.</t>
+          <t>No description provided</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Verify that an existing user's role can be successfully updated.</t>
+          <t>No description provided</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Verify that a user's status can be changed to 'Disabled'.</t>
+          <t>No description provided</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Verify that multiple users can be selected and deleted simultaneously.</t>
+          <t>No description provided</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Verify that users can be searched and found by their exact username.</t>
+          <t>No description provided</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Verify that users can be filtered by their assigned 'User Role'.</t>
+          <t>No description provided</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Verify that users can be filtered by their current 'Status' (Enabled/Disabled).</t>
+          <t>No description provided</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Verify that a 'No Records Found' message is displayed when searching for a non-existent username.</t>
+          <t>No description provided</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Verify that a user can be successfully deleted from the system.</t>
+          <t>No description provided</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
